--- a/XLibur.Tests/Resource/Examples/Misc/DataValidationWholeNumber.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/DataValidationWholeNumber.xlsx
@@ -360,91 +360,72 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:B1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:2">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B1" s="0">
+      <x:c r="B1">
         <x:v>2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="16">
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A2:A10">
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A10">
       <x:formula1>1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="notEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B2:B10">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="notEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B10">
       <x:formula1>2</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C2:C10">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C10">
       <x:formula1>3</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D2:D10">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D10">
       <x:formula1>4</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E2:E10">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E10">
       <x:formula1>5</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F2:F10">
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F10">
       <x:formula1>6</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G2:G10">
+    </x:dataValidation>
+    <x:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G10">
       <x:formula1>7</x:formula1>
       <x:formula2>8</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H2:H10">
+    <x:dataValidation type="whole" operator="notBetween" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H10">
       <x:formula1>9</x:formula1>
       <x:formula2>10</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="equal" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="A11:A20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="notEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="B11:B20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="C11:C20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="lessThan" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="D11:D20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="greaterThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="E11:E20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="lessThanOrEqual" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="F11:F20">
-      <x:formula1>$A$1</x:formula1>
-      <x:formula2/>
-    </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="G11:G20">
+    <x:dataValidation type="whole" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A11:A20">
+      <x:formula1>$A$1</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="notEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11:B20">
+      <x:formula1>$A$1</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C11:C20">
+      <x:formula1>$A$1</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="lessThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D11:D20">
+      <x:formula1>$A$1</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11:E20">
+      <x:formula1>$A$1</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11:F20">
+      <x:formula1>$A$1</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G11:G20">
       <x:formula1>$A$1</x:formula1>
       <x:formula2>$B$1</x:formula2>
     </x:dataValidation>
-    <x:dataValidation type="whole" errorStyle="stop" operator="notBetween" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="" sqref="H11:H20">
+    <x:dataValidation type="whole" operator="notBetween" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H11:H20">
       <x:formula1>$A$1</x:formula1>
       <x:formula2>$B$1</x:formula2>
     </x:dataValidation>
   </x:dataValidations>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>